--- a/other/baking_contest_application_form.xlsx
+++ b/other/baking_contest_application_form.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -538,7 +538,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>form_name</t>
+          <t>form_name_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Form Description</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>form_id_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Form Id</t>
+          <t>Form Id 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>description_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Description 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Category 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
@@ -1148,46 +1148,46 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>baking_type_choices</t>
+          <t>category_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>cakes</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cakes</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>baking_type_choices</t>
+          <t>category_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>cookies</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cookies</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>pies</t>
+          <t>cakes</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pies</t>
+          <t>cakes</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>pastries</t>
+          <t>cookies</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pastries</t>
+          <t>cookies</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>tarts</t>
+          <t>pies</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>tarts</t>
+          <t>pies</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>muffins</t>
+          <t>pastries</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>muffins</t>
+          <t>pastries</t>
         </is>
       </c>
     </row>
@@ -1267,46 +1267,46 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>tarts</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>tarts</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ingredient1_choices</t>
+          <t>baking_type_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>flour</t>
+          <t>muffins</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>flour</t>
+          <t>muffins</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ingredient1_choices</t>
+          <t>baking_type_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sugar</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sugar</t>
+          <t>bread</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>eggs</t>
+          <t>flour</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>eggs</t>
+          <t>flour</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>butter</t>
+          <t>sugar</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>butter</t>
+          <t>sugar</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>milk</t>
+          <t>eggs</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>milk</t>
+          <t>eggs</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cream</t>
+          <t>butter</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>cream</t>
+          <t>butter</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>milk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>milk</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>salt</t>
+          <t>cream</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>salt</t>
+          <t>cream</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>vanilla</t>
+          <t>water</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>vanilla</t>
+          <t>water</t>
         </is>
       </c>
     </row>
@@ -1437,46 +1437,46 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>baking_powder</t>
+          <t>salt</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>baking powder</t>
+          <t>salt</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ingredient2_choices</t>
+          <t>ingredient1_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>flour</t>
+          <t>vanilla</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>flour</t>
+          <t>vanilla</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ingredient2_choices</t>
+          <t>ingredient1_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>sugar</t>
+          <t>baking_powder</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>sugar</t>
+          <t>baking powder</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>eggs</t>
+          <t>flour</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>eggs</t>
+          <t>flour</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>butter</t>
+          <t>sugar</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>butter</t>
+          <t>sugar</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>milk</t>
+          <t>eggs</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>milk</t>
+          <t>eggs</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>cream</t>
+          <t>butter</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>cream</t>
+          <t>butter</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>milk</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>milk</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>salt</t>
+          <t>cream</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>salt</t>
+          <t>cream</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>vanilla</t>
+          <t>water</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>vanilla</t>
+          <t>water</t>
         </is>
       </c>
     </row>
@@ -1607,46 +1607,46 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>baking_powder</t>
+          <t>salt</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>baking powder</t>
+          <t>salt</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ingredient3_choices</t>
+          <t>ingredient2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>flour</t>
+          <t>vanilla</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>flour</t>
+          <t>vanilla</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ingredient3_choices</t>
+          <t>ingredient2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>sugar</t>
+          <t>baking_powder</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>sugar</t>
+          <t>baking powder</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>eggs</t>
+          <t>flour</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>eggs</t>
+          <t>flour</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>butter</t>
+          <t>sugar</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>butter</t>
+          <t>sugar</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>milk</t>
+          <t>eggs</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>milk</t>
+          <t>eggs</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>cream</t>
+          <t>butter</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>cream</t>
+          <t>butter</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>milk</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>milk</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>salt</t>
+          <t>cream</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>salt</t>
+          <t>cream</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>vanilla</t>
+          <t>water</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>vanilla</t>
+          <t>water</t>
         </is>
       </c>
     </row>
@@ -1777,46 +1777,46 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>baking_powder</t>
+          <t>salt</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>baking powder</t>
+          <t>salt</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ingredient4_choices</t>
+          <t>ingredient3_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>flour</t>
+          <t>vanilla</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>flour</t>
+          <t>vanilla</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ingredient4_choices</t>
+          <t>ingredient3_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>sugar</t>
+          <t>baking_powder</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>sugar</t>
+          <t>baking powder</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>eggs</t>
+          <t>flour</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>eggs</t>
+          <t>flour</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>butter</t>
+          <t>sugar</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>butter</t>
+          <t>sugar</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>milk</t>
+          <t>eggs</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>milk</t>
+          <t>eggs</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>cream</t>
+          <t>butter</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>cream</t>
+          <t>butter</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>milk</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>milk</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>salt</t>
+          <t>cream</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>salt</t>
+          <t>cream</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>vanilla</t>
+          <t>water</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>vanilla</t>
+          <t>water</t>
         </is>
       </c>
     </row>
@@ -1947,10 +1947,44 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>salt</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>salt</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ingredient4_choices</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>vanilla</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>vanilla</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ingredient4_choices</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>baking_powder</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>baking powder</t>
         </is>
